--- a/public/survey.xlsx
+++ b/public/survey.xlsx
@@ -11,10 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="104">
-  <si>
-    <t>CoE IE Questions Database ec23bcefde3d4c3abc2b86cb6fbdd0c6</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="103">
   <si>
     <t>Question</t>
   </si>
@@ -810,7 +807,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -820,6 +817,11 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b val="1"/>
@@ -834,7 +836,7 @@
       <name val="Helvetica Neue"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -850,6 +852,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="12"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="13"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -973,56 +981,50 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1046,6 +1048,7 @@
       <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ff3f3f3f"/>
       <rgbColor rgb="ffdbdbdb"/>
+      <rgbColor rgb="ffffffff"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1062,10 +1065,10 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="5E5E5E"/>
+        <a:srgbClr val="A7A7A7"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="D5D5D5"/>
+        <a:srgbClr val="535353"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="00A2FF"/>
@@ -1242,11 +1245,14 @@
     <a:spDef>
       <a:spPr>
         <a:solidFill>
-          <a:srgbClr val="000000"/>
+          <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:miter lim="400000"/>
+        <a:ln w="25400" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -1255,7 +1261,7 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="584200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1270,19 +1276,19 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
             <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
+              <a:srgbClr val="000000"/>
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Helvetica Neue Medium"/>
-            <a:ea typeface="Helvetica Neue Medium"/>
-            <a:cs typeface="Helvetica Neue Medium"/>
-            <a:sym typeface="Helvetica Neue Medium"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1530,12 +1536,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
-            <a:srgbClr val="000000"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="400000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -1826,7 +1832,7 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="457200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -2107,7 +2113,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H33"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="166.672" style="1" customWidth="1"/>
@@ -2121,784 +2127,769 @@
     <col min="9" max="16384" width="8.35156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.65" customHeight="1">
+    <row r="1" ht="20.25" customHeight="1">
       <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1">
+      <c r="B1" t="s" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="92.25" customHeight="1">
       <c r="A2" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s" s="3">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s" s="3">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s" s="3">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s" s="3">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s" s="3">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" ht="92.25" customHeight="1">
-      <c r="A3" t="s" s="4">
+      <c r="B2" t="s" s="4">
         <v>9</v>
       </c>
-      <c r="B3" t="s" s="6">
+      <c r="C2" t="s" s="5">
         <v>10</v>
       </c>
-      <c r="C3" t="s" s="7">
+      <c r="D2" t="s" s="5">
         <v>11</v>
       </c>
-      <c r="D3" t="s" s="7">
+      <c r="E2" t="s" s="5">
         <v>12</v>
       </c>
-      <c r="E3" t="s" s="7">
-        <v>13</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" t="s" s="7">
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" t="s" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="128.05" customHeight="1">
+      <c r="A3" t="s" s="7">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" ht="128.05" customHeight="1">
-      <c r="A4" t="s" s="9">
+      <c r="B3" t="s" s="8">
         <v>15</v>
       </c>
-      <c r="B4" t="s" s="11">
+      <c r="C3" t="s" s="9">
         <v>16</v>
       </c>
-      <c r="C4" t="s" s="12">
+      <c r="D3" t="s" s="9">
         <v>17</v>
       </c>
-      <c r="D4" t="s" s="12">
+      <c r="E3" t="s" s="9">
+        <v>17</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" ht="32.05" customHeight="1">
+      <c r="A4" t="s" s="7">
         <v>18</v>
       </c>
-      <c r="E4" t="s" s="12">
-        <v>18</v>
-      </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" t="s" s="12">
-        <v>14</v>
+      <c r="B4" t="s" s="8">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s" s="9">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s" s="9">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="9">
+        <v>21</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" t="s" s="9">
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="32.05" customHeight="1">
-      <c r="A5" t="s" s="9">
+      <c r="A5" t="s" s="7">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s" s="8">
         <v>19</v>
       </c>
-      <c r="B5" t="s" s="11">
+      <c r="C5" t="s" s="9">
         <v>20</v>
       </c>
-      <c r="C5" t="s" s="12">
+      <c r="D5" t="s" s="9">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="9">
+        <v>23</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" ht="92.05" customHeight="1">
+      <c r="A6" t="s" s="7">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s" s="8">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s" s="9">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s" s="9">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="9">
         <v>21</v>
       </c>
-      <c r="D5" t="s" s="12">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s" s="12">
-        <v>22</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="32.05" customHeight="1">
-      <c r="A6" t="s" s="9">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s" s="11">
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" ht="356.05" customHeight="1">
+      <c r="A7" t="s" s="7">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s" s="8">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="9">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s" s="9">
+        <v>29</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" ht="68.05" customHeight="1">
+      <c r="A8" t="s" s="7">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s" s="8">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s" s="9">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s" s="9">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s" s="9">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s" s="9">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="128.05" customHeight="1">
+      <c r="A9" t="s" s="7">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s" s="8">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s" s="9">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s" s="9">
+        <v>37</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" ht="92.05" customHeight="1">
+      <c r="A10" t="s" s="7">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s" s="8">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s" s="9">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s" s="9">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s" s="9">
+        <v>41</v>
+      </c>
+      <c r="G10" t="s" s="11">
+        <v>42</v>
+      </c>
+      <c r="H10" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" ht="104.05" customHeight="1">
+      <c r="A11" t="s" s="7">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s" s="8">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s" s="9">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s" s="9">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s" s="9">
+        <v>41</v>
+      </c>
+      <c r="G11" t="s" s="9">
+        <v>47</v>
+      </c>
+      <c r="H11" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" ht="56.05" customHeight="1">
+      <c r="A12" t="s" s="7">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s" s="8">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s" s="9">
         <v>20</v>
       </c>
-      <c r="C6" t="s" s="12">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s" s="12">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s" s="12">
-        <v>24</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="92.05" customHeight="1">
-      <c r="A7" t="s" s="9">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s" s="11">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s" s="12">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s" s="12">
-        <v>22</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="356.05" customHeight="1">
-      <c r="A8" t="s" s="9">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s" s="11">
+      <c r="D12" t="s" s="9">
         <v>28</v>
       </c>
-      <c r="C8" t="s" s="12">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s" s="12">
+      <c r="E12" t="s" s="9">
+        <v>46</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" ht="20.05" customHeight="1">
+      <c r="A13" t="s" s="7">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s" s="12">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s" s="9">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s" s="9">
         <v>29</v>
       </c>
-      <c r="E8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" ht="68.05" customHeight="1">
-      <c r="A9" t="s" s="9">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s" s="11">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s" s="12">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s" s="12">
+      <c r="F13" t="s" s="9">
         <v>33</v>
       </c>
-      <c r="F9" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="G9" t="s" s="12">
-        <v>35</v>
-      </c>
-      <c r="H9" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" ht="128.05" customHeight="1">
-      <c r="A10" t="s" s="9">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s" s="11">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s" s="12">
-        <v>29</v>
-      </c>
-      <c r="E10" t="s" s="12">
-        <v>38</v>
-      </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" ht="92.05" customHeight="1">
-      <c r="A11" t="s" s="9">
-        <v>39</v>
-      </c>
-      <c r="B11" t="s" s="11">
-        <v>40</v>
-      </c>
-      <c r="C11" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s" s="12">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s" s="12">
+      <c r="G13" t="s" s="9">
+        <v>53</v>
+      </c>
+      <c r="H13" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" ht="44.05" customHeight="1">
+      <c r="A14" t="s" s="7">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s" s="8">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s" s="9">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s" s="9">
+        <v>57</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" ht="44.05" customHeight="1">
+      <c r="A15" t="s" s="7">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s" s="8">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s" s="9">
+        <v>56</v>
+      </c>
+      <c r="E15" t="s" s="9">
+        <v>57</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" ht="32.05" customHeight="1">
+      <c r="A16" t="s" s="7">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s" s="8">
+        <v>60</v>
+      </c>
+      <c r="C16" t="s" s="9">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s" s="9">
+        <v>61</v>
+      </c>
+      <c r="E16" t="s" s="9">
+        <v>62</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" ht="32.05" customHeight="1">
+      <c r="A17" t="s" s="7">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s" s="8">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s" s="9">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s" s="9">
+        <v>61</v>
+      </c>
+      <c r="E17" t="s" s="9">
+        <v>64</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" ht="20.05" customHeight="1">
+      <c r="A18" t="s" s="7">
+        <v>65</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" t="s" s="9">
+        <v>66</v>
+      </c>
+      <c r="D18" t="s" s="9">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s" s="9">
+        <v>68</v>
+      </c>
+      <c r="F18" t="s" s="9">
         <v>41</v>
       </c>
-      <c r="F11" t="s" s="12">
-        <v>42</v>
-      </c>
-      <c r="G11" t="s" s="14">
-        <v>43</v>
-      </c>
-      <c r="H11" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" ht="104.05" customHeight="1">
-      <c r="A12" t="s" s="9">
-        <v>44</v>
-      </c>
-      <c r="B12" t="s" s="11">
-        <v>45</v>
-      </c>
-      <c r="C12" t="s" s="12">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s" s="12">
-        <v>29</v>
-      </c>
-      <c r="E12" t="s" s="12">
-        <v>47</v>
-      </c>
-      <c r="F12" t="s" s="12">
-        <v>42</v>
-      </c>
-      <c r="G12" t="s" s="12">
-        <v>48</v>
-      </c>
-      <c r="H12" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" ht="56.05" customHeight="1">
-      <c r="A13" t="s" s="9">
-        <v>49</v>
-      </c>
-      <c r="B13" t="s" s="11">
-        <v>50</v>
-      </c>
-      <c r="C13" t="s" s="12">
-        <v>21</v>
-      </c>
-      <c r="D13" t="s" s="12">
-        <v>29</v>
-      </c>
-      <c r="E13" t="s" s="12">
-        <v>47</v>
-      </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" t="s" s="9">
-        <v>51</v>
-      </c>
-      <c r="B14" t="s" s="10">
+      <c r="G18" t="s" s="9">
+        <v>69</v>
+      </c>
+      <c r="H18" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" ht="176.05" customHeight="1">
+      <c r="A19" t="s" s="7">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s" s="8">
+        <v>71</v>
+      </c>
+      <c r="C19" t="s" s="9">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s" s="9">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s" s="9">
+        <v>72</v>
+      </c>
+      <c r="F19" t="s" s="9">
+        <v>33</v>
+      </c>
+      <c r="G19" t="s" s="9">
+        <v>73</v>
+      </c>
+      <c r="H19" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" ht="32.05" customHeight="1">
+      <c r="A20" t="s" s="7">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s" s="8">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s" s="9">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s" s="9">
+        <v>67</v>
+      </c>
+      <c r="E20" t="s" s="9">
+        <v>75</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" ht="116.05" customHeight="1">
+      <c r="A21" t="s" s="7">
+        <v>76</v>
+      </c>
+      <c r="B21" t="s" s="8">
+        <v>77</v>
+      </c>
+      <c r="C21" t="s" s="9">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s" s="9">
+        <v>67</v>
+      </c>
+      <c r="E21" t="s" s="9">
+        <v>75</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" ht="68.05" customHeight="1">
+      <c r="A22" t="s" s="7">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s" s="8">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s" s="9">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s" s="9">
+        <v>67</v>
+      </c>
+      <c r="E22" t="s" s="9">
+        <v>75</v>
+      </c>
+      <c r="F22" t="s" s="9">
+        <v>41</v>
+      </c>
+      <c r="G22" t="s" s="9">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" ht="116.05" customHeight="1">
+      <c r="A23" t="s" s="7">
+        <v>81</v>
+      </c>
+      <c r="B23" t="s" s="8">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s" s="9">
         <v>52</v>
       </c>
-      <c r="C14" t="s" s="12">
-        <v>53</v>
-      </c>
-      <c r="D14" t="s" s="12">
-        <v>29</v>
-      </c>
-      <c r="E14" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="F14" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="G14" t="s" s="12">
-        <v>54</v>
-      </c>
-      <c r="H14" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" ht="44.05" customHeight="1">
-      <c r="A15" t="s" s="9">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s" s="11">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s" s="12">
-        <v>53</v>
-      </c>
-      <c r="D15" t="s" s="12">
-        <v>57</v>
-      </c>
-      <c r="E15" t="s" s="12">
-        <v>58</v>
-      </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" ht="44.05" customHeight="1">
-      <c r="A16" t="s" s="9">
-        <v>59</v>
-      </c>
-      <c r="B16" t="s" s="11">
-        <v>56</v>
-      </c>
-      <c r="C16" t="s" s="12">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s" s="12">
-        <v>57</v>
-      </c>
-      <c r="E16" t="s" s="12">
-        <v>58</v>
-      </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" ht="32.05" customHeight="1">
-      <c r="A17" t="s" s="9">
+      <c r="D23" t="s" s="9">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s" s="9">
+        <v>68</v>
+      </c>
+      <c r="F23" t="s" s="9">
+        <v>41</v>
+      </c>
+      <c r="G23" t="s" s="9">
+        <v>83</v>
+      </c>
+      <c r="H23" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" ht="56.05" customHeight="1">
+      <c r="A24" t="s" s="7">
+        <v>84</v>
+      </c>
+      <c r="B24" t="s" s="8">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="D24" t="s" s="9">
+        <v>86</v>
+      </c>
+      <c r="E24" t="s" s="9">
+        <v>12</v>
+      </c>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" ht="44.05" customHeight="1">
+      <c r="A25" t="s" s="7">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s" s="8">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="D25" t="s" s="9">
+        <v>86</v>
+      </c>
+      <c r="E25" t="s" s="9">
+        <v>89</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" ht="32.05" customHeight="1">
+      <c r="A26" t="s" s="7">
+        <v>90</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" t="s" s="9">
+        <v>66</v>
+      </c>
+      <c r="D26" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="E26" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="F26" t="s" s="9">
+        <v>41</v>
+      </c>
+      <c r="G26" t="s" s="11">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" ht="32.05" customHeight="1">
+      <c r="A27" t="s" s="14">
+        <v>93</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" t="s" s="9">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="E27" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="F27" t="s" s="9">
+        <v>41</v>
+      </c>
+      <c r="G27" t="s" s="11">
+        <v>92</v>
+      </c>
+      <c r="H27" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" ht="32.05" customHeight="1">
+      <c r="A28" t="s" s="14">
+        <v>94</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" t="s" s="9">
+        <v>66</v>
+      </c>
+      <c r="D28" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="E28" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="F28" t="s" s="9">
+        <v>41</v>
+      </c>
+      <c r="G28" t="s" s="11">
+        <v>92</v>
+      </c>
+      <c r="H28" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" ht="44.05" customHeight="1">
+      <c r="A29" t="s" s="14">
+        <v>95</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" t="s" s="9">
+        <v>66</v>
+      </c>
+      <c r="D29" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="E29" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="F29" t="s" s="9">
+        <v>33</v>
+      </c>
+      <c r="G29" t="s" s="11">
+        <v>96</v>
+      </c>
+      <c r="H29" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" ht="20.05" customHeight="1">
+      <c r="A30" t="s" s="7">
+        <v>97</v>
+      </c>
+      <c r="B30" t="s" s="12">
+        <v>98</v>
+      </c>
+      <c r="C30" t="s" s="9">
+        <v>16</v>
+      </c>
+      <c r="D30" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="E30" t="s" s="9">
+        <v>99</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" ht="32.05" customHeight="1">
+      <c r="A31" t="s" s="7">
+        <v>100</v>
+      </c>
+      <c r="B31" t="s" s="8">
         <v>60</v>
       </c>
-      <c r="B17" t="s" s="11">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s" s="12">
-        <v>21</v>
-      </c>
-      <c r="D17" t="s" s="12">
-        <v>62</v>
-      </c>
-      <c r="E17" t="s" s="12">
-        <v>63</v>
-      </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" ht="32.05" customHeight="1">
-      <c r="A18" t="s" s="9">
-        <v>64</v>
-      </c>
-      <c r="B18" t="s" s="11">
-        <v>61</v>
-      </c>
-      <c r="C18" t="s" s="12">
-        <v>21</v>
-      </c>
-      <c r="D18" t="s" s="12">
-        <v>62</v>
-      </c>
-      <c r="E18" t="s" s="12">
-        <v>65</v>
-      </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" t="s" s="9">
+      <c r="C31" t="s" s="9">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="E31" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="F31" t="s" s="9">
+        <v>33</v>
+      </c>
+      <c r="G31" t="s" s="9">
+        <v>101</v>
+      </c>
+      <c r="H31" t="s" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" ht="20.05" customHeight="1">
+      <c r="A32" t="s" s="7">
+        <v>102</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" t="s" s="9">
         <v>66</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="D19" t="s" s="12">
-        <v>68</v>
-      </c>
-      <c r="E19" t="s" s="12">
-        <v>69</v>
-      </c>
-      <c r="F19" t="s" s="12">
-        <v>42</v>
-      </c>
-      <c r="G19" t="s" s="12">
-        <v>70</v>
-      </c>
-      <c r="H19" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" ht="176.05" customHeight="1">
-      <c r="A20" t="s" s="9">
-        <v>71</v>
-      </c>
-      <c r="B20" t="s" s="11">
-        <v>72</v>
-      </c>
-      <c r="C20" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="D20" t="s" s="12">
-        <v>68</v>
-      </c>
-      <c r="E20" t="s" s="12">
-        <v>73</v>
-      </c>
-      <c r="F20" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="G20" t="s" s="12">
-        <v>74</v>
-      </c>
-      <c r="H20" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" ht="32.05" customHeight="1">
-      <c r="A21" t="s" s="9">
-        <v>75</v>
-      </c>
-      <c r="B21" t="s" s="11">
-        <v>61</v>
-      </c>
-      <c r="C21" t="s" s="12">
-        <v>21</v>
-      </c>
-      <c r="D21" t="s" s="12">
-        <v>68</v>
-      </c>
-      <c r="E21" t="s" s="12">
-        <v>76</v>
-      </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" ht="116.05" customHeight="1">
-      <c r="A22" t="s" s="9">
-        <v>77</v>
-      </c>
-      <c r="B22" t="s" s="11">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s" s="12">
-        <v>21</v>
-      </c>
-      <c r="D22" t="s" s="12">
-        <v>68</v>
-      </c>
-      <c r="E22" t="s" s="12">
-        <v>76</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" ht="68.05" customHeight="1">
-      <c r="A23" t="s" s="9">
-        <v>79</v>
-      </c>
-      <c r="B23" t="s" s="11">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="D23" t="s" s="12">
-        <v>68</v>
-      </c>
-      <c r="E23" t="s" s="12">
-        <v>76</v>
-      </c>
-      <c r="F23" t="s" s="12">
-        <v>42</v>
-      </c>
-      <c r="G23" t="s" s="12">
-        <v>81</v>
-      </c>
-      <c r="H23" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" ht="116.05" customHeight="1">
-      <c r="A24" t="s" s="9">
-        <v>82</v>
-      </c>
-      <c r="B24" t="s" s="11">
-        <v>83</v>
-      </c>
-      <c r="C24" t="s" s="12">
-        <v>53</v>
-      </c>
-      <c r="D24" t="s" s="12">
-        <v>68</v>
-      </c>
-      <c r="E24" t="s" s="12">
-        <v>69</v>
-      </c>
-      <c r="F24" t="s" s="12">
-        <v>42</v>
-      </c>
-      <c r="G24" t="s" s="12">
-        <v>84</v>
-      </c>
-      <c r="H24" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" ht="56.05" customHeight="1">
-      <c r="A25" t="s" s="9">
-        <v>85</v>
-      </c>
-      <c r="B25" t="s" s="11">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s" s="12">
-        <v>53</v>
-      </c>
-      <c r="D25" t="s" s="12">
-        <v>87</v>
-      </c>
-      <c r="E25" t="s" s="12">
-        <v>13</v>
-      </c>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" ht="44.05" customHeight="1">
-      <c r="A26" t="s" s="9">
-        <v>88</v>
-      </c>
-      <c r="B26" t="s" s="11">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s" s="12">
-        <v>53</v>
-      </c>
-      <c r="D26" t="s" s="12">
-        <v>87</v>
-      </c>
-      <c r="E26" t="s" s="12">
-        <v>90</v>
-      </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" ht="32.05" customHeight="1">
-      <c r="A27" t="s" s="9">
+      <c r="D32" t="s" s="9">
         <v>91</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="D27" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="E27" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="F27" t="s" s="12">
-        <v>42</v>
-      </c>
-      <c r="G27" t="s" s="14">
-        <v>93</v>
-      </c>
-      <c r="H27" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" ht="32.05" customHeight="1">
-      <c r="A28" t="s" s="16">
-        <v>94</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="D28" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="E28" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="F28" t="s" s="12">
-        <v>42</v>
-      </c>
-      <c r="G28" t="s" s="14">
-        <v>93</v>
-      </c>
-      <c r="H28" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" ht="32.05" customHeight="1">
-      <c r="A29" t="s" s="16">
-        <v>95</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="D29" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="E29" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="F29" t="s" s="12">
-        <v>42</v>
-      </c>
-      <c r="G29" t="s" s="14">
-        <v>93</v>
-      </c>
-      <c r="H29" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" ht="44.05" customHeight="1">
-      <c r="A30" t="s" s="16">
-        <v>96</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="D30" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="E30" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="F30" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="G30" t="s" s="14">
-        <v>97</v>
-      </c>
-      <c r="H30" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" ht="20.05" customHeight="1">
-      <c r="A31" t="s" s="9">
-        <v>98</v>
-      </c>
-      <c r="B31" t="s" s="10">
-        <v>99</v>
-      </c>
-      <c r="C31" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="D31" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="E31" t="s" s="12">
-        <v>100</v>
-      </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" ht="32.05" customHeight="1">
-      <c r="A32" t="s" s="9">
-        <v>101</v>
-      </c>
-      <c r="B32" t="s" s="11">
-        <v>61</v>
-      </c>
-      <c r="C32" t="s" s="12">
-        <v>21</v>
-      </c>
-      <c r="D32" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="E32" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="F32" t="s" s="12">
-        <v>34</v>
-      </c>
-      <c r="G32" t="s" s="12">
-        <v>102</v>
-      </c>
-      <c r="H32" t="s" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" ht="20.05" customHeight="1">
-      <c r="A33" t="s" s="9">
-        <v>103</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" t="s" s="12">
-        <v>67</v>
-      </c>
-      <c r="D33" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="E33" t="s" s="12">
-        <v>92</v>
-      </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" t="s" s="12">
-        <v>14</v>
+      <c r="E32" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" t="s" s="9">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G9" r:id="rId1" location="" tooltip="" display="https://www.notion.so/For-what-purpose-do-you-use-each-service-143d10e1ec8780ea8566e053af8f1825?pvs=21"/>
-    <hyperlink ref="G11" r:id="rId2" location="" tooltip="" display="https://www.notion.so/After-working-with-Company-service-what-digital-tools-and-services-did-you-use-for-your-busines-137d10e1ec878034bb98cc02f733d6b8?pvs=21"/>
-    <hyperlink ref="G12" r:id="rId3" location="" tooltip="" display="https://www.notion.so/In-what-year-was-this-most-recent-line-of-credit-or-loan-approved-125d10e1ec87808bb67ad1199a22c90d?pvs=21"/>
-    <hyperlink ref="G14" r:id="rId4" location="" tooltip="" display="https://www.notion.so/If-Yes-How-has-it-changed-ability-to-use-digital-tools-9a7a517e6d5447f9a649fe7c92b9c7e6?pvs=21"/>
-    <hyperlink ref="G19" r:id="rId5" location="" tooltip="" display="https://www.notion.so/Have-you-experienced-any-of-the-following-EVENTS-RELATED-TO-YOUR-BUSINESS-since-the-last-time-we-sp-144d10e1ec87809f8bd0ce14470aa0e1?pvs=21"/>
-    <hyperlink ref="G20" r:id="rId6" location="" tooltip="" display="https://www.notion.so/Did-you-face-any-financial-loss-due-to-144d10e1ec87806bb02bc120871622c7?pvs=21"/>
-    <hyperlink ref="G23" r:id="rId7" location="" tooltip="" display="https://www.notion.so/What-measures-did-you-use-to-cope-with-the-shock-c63d4d6d86ce4f7b8f3375a6254aa3cc?pvs=21"/>
-    <hyperlink ref="G24" r:id="rId8" location="" tooltip="" display="https://www.notion.so/How-long-did-the-shock-last-305b547bf51c464d8df1848891c573d1?pvs=21"/>
-    <hyperlink ref="G27" r:id="rId9" location="" tooltip="" display="https://www.notion.so/On-a-scale-of-0-10-how-likely-are-you-to-recommend-to-a-friend-or-family-member-where-0-is-not-a-137d10e1ec8780068313e29eba42ee26?pvs=21"/>
-    <hyperlink ref="G28" r:id="rId10" location="" tooltip="" display="https://www.notion.so/On-a-scale-of-0-10-how-likely-are-you-to-recommend-to-a-friend-or-family-member-where-0-is-not-a-137d10e1ec8780068313e29eba42ee26?pvs=21"/>
-    <hyperlink ref="G29" r:id="rId11" location="" tooltip="" display="https://www.notion.so/On-a-scale-of-0-10-how-likely-are-you-to-recommend-to-a-friend-or-family-member-where-0-is-not-a-137d10e1ec8780068313e29eba42ee26?pvs=21"/>
-    <hyperlink ref="G30" r:id="rId12" location="" tooltip="" display="https://www.notion.so/If-9-10-What-specifically-about-Company-program-service-would-cause-you-to-recommend-it-to-a-fri-137d10e1ec87804c8d1ce65155d6abbb?pvs=21"/>
-    <hyperlink ref="G32" r:id="rId13" location="" tooltip="" display="https://www.notion.so/Kindly-share-challenges-you-re-facing-7ddf28e392964c65b82834ca9b22e2d8?pvs=21"/>
+    <hyperlink ref="G8" r:id="rId1" location="" tooltip="" display="For what purpose do you use each service? (https://www.notion.so/For-what-purpose-do-you-use-each-service-143d10e1ec8780ea8566e053af8f1825?pvs=21)"/>
+    <hyperlink ref="G10" r:id="rId2" location="" tooltip="" display="After working with [Company/service], what digital&#10;  tools and services did you use for your business? Select all that apply. (https://www.notion.so/After-working-with-Company-service-what-digital-tools-and-services-did-you-use-for-your-busines-137d10e1ec878034bb98cc02f733d6b8?pvs=21)"/>
+    <hyperlink ref="G11" r:id="rId3" location="" tooltip="" display="In what year was this most recent line of credit or loan approved?  (https://www.notion.so/In-what-year-was-this-most-recent-line-of-credit-or-loan-approved-125d10e1ec87808bb67ad1199a22c90d?pvs=21)"/>
+    <hyperlink ref="G13" r:id="rId4" location="" tooltip="" display="[If Yes] How has it changed: (ability to use digital tools)  (https://www.notion.so/If-Yes-How-has-it-changed-ability-to-use-digital-tools-9a7a517e6d5447f9a649fe7c92b9c7e6?pvs=21)"/>
+    <hyperlink ref="G18" r:id="rId5" location="" tooltip="" display="Have you experienced any of the following EVENTS RELATED TO YOUR BUSINESS [since the last time we spoke/since engaging with XXX company/service]? (https://www.notion.so/Have-you-experienced-any-of-the-following-EVENTS-RELATED-TO-YOUR-BUSINESS-since-the-last-time-we-sp-144d10e1ec87809f8bd0ce14470aa0e1?pvs=21)"/>
+    <hyperlink ref="G19" r:id="rId6" location="" tooltip="" display="Did you face any financial loss due to? (https://www.notion.so/Did-you-face-any-financial-loss-due-to-144d10e1ec87806bb02bc120871622c7?pvs=21), How much did you lose due to this? (https://www.notion.so/How-much-did-you-lose-due-to-this-144d10e1ec87809b9027f447be780df3?pvs=21), How did you respond to {0}? (https://www.notion.so/How-did-you-respond-to-0-144d10e1ec878062affbdcfd9a49fb17?pvs=21)"/>
+    <hyperlink ref="G22" r:id="rId7" location="" tooltip="" display="What measures did you use to cope with the shock? (https://www.notion.so/What-measures-did-you-use-to-cope-with-the-shock-c63d4d6d86ce4f7b8f3375a6254aa3cc?pvs=21)"/>
+    <hyperlink ref="G23" r:id="rId8" location="" tooltip="" display="How long did the shock last? (https://www.notion.so/How-long-did-the-shock-last-305b547bf51c464d8df1848891c573d1?pvs=21)"/>
+    <hyperlink ref="G26" r:id="rId9" location="" tooltip="" display="On a scale of 0-10, how likely are you to recommend to a friend or&#10;  family member, where 0 is not at all likely and 10 is extremely likely? (https://www.notion.so/On-a-scale-of-0-10-how-likely-are-you-to-recommend-to-a-friend-or-family-member-where-0-is-not-a-137d10e1ec8780068313e29eba42ee26?pvs=21)"/>
+    <hyperlink ref="G27" r:id="rId10" location="" tooltip="" display="On a scale of 0-10, how likely are you to recommend to a friend or&#10;  family member, where 0 is not at all likely and 10 is extremely likely? (https://www.notion.so/On-a-scale-of-0-10-how-likely-are-you-to-recommend-to-a-friend-or-family-member-where-0-is-not-a-137d10e1ec8780068313e29eba42ee26?pvs=21)"/>
+    <hyperlink ref="G28" r:id="rId11" location="" tooltip="" display="On a scale of 0-10, how likely are you to recommend to a friend or&#10;  family member, where 0 is not at all likely and 10 is extremely likely? (https://www.notion.so/On-a-scale-of-0-10-how-likely-are-you-to-recommend-to-a-friend-or-family-member-where-0-is-not-a-137d10e1ec8780068313e29eba42ee26?pvs=21)"/>
+    <hyperlink ref="G29" r:id="rId12" location="" tooltip="" display="[If 9-10:] What specifically about [Company/program/service] would cause you to recommend it to a friend or family member? (https://www.notion.so/If-9-10-What-specifically-about-Company-program-service-would-cause-you-to-recommend-it-to-a-fri-137d10e1ec87804c8d1ce65155d6abbb?pvs=21), [If 7-8:] What specifically about [Company/program/service]  caused you to give&#10;  it the score that you did? (https://www.notion.so/If-7-8-What-specifically-about-Company-program-service-caused-you-to-give-it-the-score-that-y-137d10e1ec878037b7efe5620da8e9b0?pvs=21), [If 0-6:] What actions could [Company/program/service] take to make you more&#10;  likely to recommend them to a friend or family member? (https://www.notion.so/If-0-6-What-actions-could-Company-program-service-take-to-make-you-more-likely-to-recommend-th-137d10e1ec878015a86fc32bd90d6d49?pvs=21)"/>
+    <hyperlink ref="G31" r:id="rId13" location="" tooltip="" display="Kindly share challenges you're facing. (https://www.notion.so/Kindly-share-challenges-you-re-facing-7ddf28e392964c65b82834ca9b22e2d8?pvs=21)"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
